--- a/SGC-CKN/Excel/d82cdb4b-6358-44ce-b9fe-3d5aba52e48f_Lô_CT-02_P7-33_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/d82cdb4b-6358-44ce-b9fe-3d5aba52e48f_Lô_CT-02_P7-33_D800_10-03-2026.xlsx
@@ -1242,7 +1242,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.7</v>
@@ -1251,10 +1251,10 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="5">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="J11" s="8">
-        <v>1.97</v>
+        <v>4.47</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1724,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.7</v>
@@ -1733,10 +1733,10 @@
         <v>1.5</v>
       </c>
       <c r="H2" s="5">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="I2" s="8">
-        <v>1.97</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2014,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-45.1</v>
@@ -2023,10 +2023,10 @@
         <v>15.92</v>
       </c>
       <c r="H12" s="40">
-        <v>41.35</v>
+        <v>45.1</v>
       </c>
       <c r="I12" s="40">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/d82cdb4b-6358-44ce-b9fe-3d5aba52e48f_Lô_CT-02_P7-33_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/d82cdb4b-6358-44ce-b9fe-3d5aba52e48f_Lô_CT-02_P7-33_D800_10-03-2026.xlsx
@@ -386,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -396,12 +396,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -572,17 +572,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1242,7 +1242,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="G11" s="5">
         <v>-6.7</v>
@@ -1251,10 +1251,10 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="5">
-        <v>6.7</v>
+        <v>10.43</v>
       </c>
       <c r="J11" s="8">
-        <v>4.47</v>
+        <v>6.95</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1288,7 +1288,7 @@
       <c r="I12" s="9">
         <v>2.72</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="12">
         <v>2.77</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1296,37 +1296,37 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>-9.42</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>-17.42</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>1.32</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <v>8</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="8">
         <v>6.08</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="I14" s="16">
         <v>3.9</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="12">
         <v>3.6</v>
       </c>
       <c r="K14" s="17" t="s">
@@ -1393,7 +1393,7 @@
       <c r="I15" s="19">
         <v>4.08</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="12">
         <v>2.35</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1428,7 +1428,7 @@
       <c r="I16" s="22">
         <v>10.4</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="12">
         <v>4.66</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1463,7 +1463,7 @@
       <c r="I17" s="25">
         <v>2.04</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="12">
         <v>2.23</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1498,7 +1498,7 @@
       <c r="I18" s="28">
         <v>1.76</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="12">
         <v>1.11</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1533,7 +1533,7 @@
       <c r="I19" s="31">
         <v>4.42</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="12">
         <v>1.78</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1724,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="F2" s="5">
         <v>-6.7</v>
@@ -1733,10 +1733,10 @@
         <v>1.5</v>
       </c>
       <c r="H2" s="5">
-        <v>6.7</v>
+        <v>10.43</v>
       </c>
       <c r="I2" s="8">
-        <v>4.47</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1764,36 +1764,36 @@
       <c r="H3" s="9">
         <v>2.72</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="12">
         <v>2.77</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-9.42</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-17.42</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="13">
         <v>1.32</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="13">
         <v>8</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="8">
         <v>6.08</v>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       <c r="H5" s="16">
         <v>3.9</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="12">
         <v>3.6</v>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       <c r="H6" s="19">
         <v>4.08</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="12">
         <v>2.35</v>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       <c r="H7" s="22">
         <v>10.4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="12">
         <v>4.66</v>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       <c r="H8" s="25">
         <v>2.04</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="12">
         <v>2.23</v>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       <c r="H9" s="28">
         <v>1.76</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="12">
         <v>1.11</v>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       <c r="H10" s="31">
         <v>4.42</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="12">
         <v>1.78</v>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="F12" s="40">
         <v>-45.1</v>
@@ -2023,10 +2023,10 @@
         <v>15.92</v>
       </c>
       <c r="H12" s="40">
-        <v>45.1</v>
+        <v>48.83</v>
       </c>
       <c r="I12" s="40">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
     </row>
   </sheetData>
